--- a/Tools/DataTablesTool/DataTables/Datas_Gen/#Sound.xlsx
+++ b/Tools/DataTablesTool/DataTables/Datas_Gen/#Sound.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\ProjectGroup\CommandoRobot\Tools\DataTablesTool\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\ProjectGroup\CommandoRobot\Tools\DataTablesTool\DataTables\Datas_Gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="22185" windowHeight="9015"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -169,13 +169,28 @@
     <t>Enemy Projectile Hit 2</t>
   </si>
   <si>
-    <t>Player Projectile</t>
-  </si>
-  <si>
     <t>Player Projectile Hit</t>
   </si>
   <si>
     <t>Player Dead</t>
+  </si>
+  <si>
+    <t>WeaponRifle</t>
+  </si>
+  <si>
+    <t>WeaponShotgun</t>
+  </si>
+  <si>
+    <t>WeaponRPG</t>
+  </si>
+  <si>
+    <t>WeaponEnergy</t>
+  </si>
+  <si>
+    <t>WeaponSniper</t>
+  </si>
+  <si>
+    <t>WeaponCrossbow</t>
   </si>
 </sst>
 </file>
@@ -644,148 +659,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1137,13 +1152,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="79.875" customWidth="1"/>
-    <col min="4" max="4" width="24.5" customWidth="1"/>
-    <col min="5" max="5" width="11.375" customWidth="1"/>
-    <col min="10" max="10" width="17.625" customWidth="1"/>
+    <col min="3" max="3" width="40.5" customWidth="1"/>
+    <col min="4" max="4" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1336,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1377,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1418,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1436,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -1459,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1477,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -1500,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1518,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -1541,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1559,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -1582,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1600,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -1623,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1641,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -1664,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1682,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -1693,7 +1706,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="B14">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="C14" t="s">
         <v>45</v>
@@ -1705,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>1.5</v>
+        <v>0.65</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1723,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -1734,7 +1747,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="B15">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1764,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -1775,7 +1788,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="B16">
-        <v>2103</v>
+        <v>2201</v>
       </c>
       <c r="C16" t="s">
         <v>47</v>
@@ -1805,12 +1818,217 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17">
+        <v>2202</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0.8</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>100</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18">
+        <v>2203</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19">
+        <v>2204</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0.75</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>100</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20">
+        <v>2205</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>100</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21">
+        <v>2206</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0.9</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="N21">
         <v>1</v>
       </c>
     </row>

--- a/Tools/DataTablesTool/DataTables/Datas_Gen/#Sound.xlsx
+++ b/Tools/DataTablesTool/DataTables/Datas_Gen/#Sound.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\ProjectGroup\CommandoRobot\Tools\DataTablesTool\DataTables\Datas_Gen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\ProjectGroup\CommandoRobot\Tools\DataTablesTool\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -191,6 +191,27 @@
   </si>
   <si>
     <t>WeaponCrossbow</t>
+  </si>
+  <si>
+    <t>GrenadeLanuch</t>
+  </si>
+  <si>
+    <t>bullet_hit_1</t>
+  </si>
+  <si>
+    <t>bullet_hit_2</t>
+  </si>
+  <si>
+    <t>bullet_hit_3</t>
+  </si>
+  <si>
+    <t>bullet_hit_4</t>
+  </si>
+  <si>
+    <t>grenade_hit</t>
+  </si>
+  <si>
+    <t>bullet_hit_5</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="40.5" customWidth="1"/>
@@ -1349,7 +1370,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1390,7 +1411,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1554,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1595,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1841,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1923,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1964,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2029,6 +2050,293 @@
         <v>100</v>
       </c>
       <c r="N21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22">
+        <v>2207</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23">
+        <v>2208</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>100</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24">
+        <v>2209</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>100</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25">
+        <v>2210</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0.2</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26">
+        <v>2211</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27">
+        <v>2212</v>
+      </c>
+      <c r="C27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>100</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28">
+        <v>2213</v>
+      </c>
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0.15</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>100</v>
+      </c>
+      <c r="N28">
         <v>1</v>
       </c>
     </row>

--- a/Tools/DataTablesTool/DataTables/Datas_Gen/#Sound.xlsx
+++ b/Tools/DataTablesTool/DataTables/Datas_Gen/#Sound.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -212,6 +212,15 @@
   </si>
   <si>
     <t>bullet_hit_5</t>
+  </si>
+  <si>
+    <t>coin</t>
+  </si>
+  <si>
+    <t>weapon_reward</t>
+  </si>
+  <si>
+    <t>health</t>
   </si>
 </sst>
 </file>
@@ -1173,11 +1182,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="40.5" customWidth="1"/>
     <col min="4" max="4" width="19.5" customWidth="1"/>
+    <col min="9" max="9" width="15.5416666666667" customWidth="1"/>
+    <col min="10" max="10" width="13.2583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1783,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -2337,6 +2348,129 @@
         <v>100</v>
       </c>
       <c r="N28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29">
+        <v>2214</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0.2</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>100</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30">
+        <v>2215</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>100</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31">
+        <v>2216</v>
+      </c>
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
         <v>1</v>
       </c>
     </row>
